--- a/healthcare_surveys/035_health_supplement_virtual_advisor--healthcare_surveys.xlsx
+++ b/healthcare_surveys/035_health_supplement_virtual_advisor--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -817,12 +817,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>improve_mental_clarity</t>
+          <t>improve_focus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Improve Mental Clarity</t>
+          <t>Improve Focus</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>improve_focus</t>
+          <t>improve_mood</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Improve Focus</t>
+          <t>Improve Mood</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>improve_mood</t>
+          <t>improve_skin_health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Improve Mood</t>
+          <t>Improve Skin Health</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>improve_skin_health</t>
+          <t>improve_hair_growth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Improve Skin Health</t>
+          <t>Improve Hair Growth</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>improve_hair_growth</t>
+          <t>improve_nervous_system</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Improve Hair Growth</t>
+          <t>Improve Nervous System</t>
         </is>
       </c>
     </row>
@@ -902,29 +902,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>improve_nervous_system</t>
+          <t>improve_immune_system</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Improve Nervous System</t>
+          <t>Improve Immune System</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>health_goals_choices</t>
+          <t>preferred_supplement_types_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>improve_immune_system</t>
+          <t>vitamin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Improve Immune System</t>
+          <t>Vitamin</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vitamin</t>
+          <t>herbal_supplement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vitamin</t>
+          <t>Herbal Supplement</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>herbal_supplement</t>
+          <t>probiotic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Herbal Supplement</t>
+          <t>Probiotic</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>probiotic</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Probiotic</t>
+          <t>Mineral</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mineral</t>
+          <t>essential_oil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mineral</t>
+          <t>Essential Oil</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>essential_oil</t>
+          <t>food_supplement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Essential Oil</t>
+          <t>Food Supplement</t>
         </is>
       </c>
     </row>
@@ -1021,29 +1021,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>food_supplement</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Food Supplement</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>preferred_supplement_types_choices</t>
+          <t>preferred_supplement_brands_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>brand_a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Brand A</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>brand_a</t>
+          <t>brand_b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brand A</t>
+          <t>Brand B</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>brand_b</t>
+          <t>brand_c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brand B</t>
+          <t>Brand C</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>brand_c</t>
+          <t>brand_d</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brand C</t>
+          <t>Brand D</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>brand_d</t>
+          <t>brand_e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brand D</t>
+          <t>Brand E</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>brand_e</t>
+          <t>brand_f</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brand E</t>
+          <t>Brand F</t>
         </is>
       </c>
     </row>
@@ -1140,27 +1140,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>brand_f</t>
+          <t>brand_g</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Brand F</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>preferred_supplement_brands_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>brand_g</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Brand G</t>
         </is>
